--- a/out/North_Fleet_Lub_Oil_Requisition.xlsx
+++ b/out/North_Fleet_Lub_Oil_Requisition.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="178">
   <si>
     <r>
       <rPr>
@@ -398,6 +398,74 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">1 PAIL – TMC Lube Plus (L)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">← 가정값</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: P/N 301020 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급분</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 5 PAILS = 94.5 L, 4 PAILS = 75.6 L (</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 제공 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 1 PAIL = 18.9 L)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">No.</t>
   </si>
   <si>
@@ -606,6 +674,40 @@
       </rPr>
       <t xml:space="preserve">확인 필요</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공급분은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TMC MARINE COMPRESSOR LUBE PLUS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">행 참조</t>
+    </r>
   </si>
   <si>
     <r>
@@ -644,7 +746,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(16) – </t>
+      <t xml:space="preserve">(17) – </t>
     </r>
     <r>
       <rPr>
@@ -693,6 +795,53 @@
     <t xml:space="preserve">PRESLIA 68</t>
   </si>
   <si>
+    <t xml:space="preserve">TMC MARINE COMPRESSOR LUBE PLUS (P/N 301020)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이번 공급분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Valley 5 / Ocean 5 / Moon 4 PAILS) – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(ROB)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 반영</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">VISGA 15</t>
   </si>
   <si>
@@ -1753,41 +1902,54 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(0)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">해당 없음 – 원본에 청구 없는 품목 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">(1)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">4 PAILS (75.6 LT)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이번 공급분 → 재고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(ROB) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">반영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">청구 없음</t>
     </r>
   </si>
   <si>
@@ -1940,6 +2102,9 @@
   </si>
   <si>
     <t xml:space="preserve">ROB 70 Lit. Required for scheduled maintenenace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 PAILS (94.5 LT)</t>
   </si>
   <si>
     <t xml:space="preserve">NORTH VALLEY – LUB OIL REQUISITION</t>
@@ -2053,7 +2218,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[=0]\-;[&gt;=1000]#,##0;General"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2150,21 +2315,6 @@
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2247,7 +2397,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2292,6 +2442,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2302,14 +2456,6 @@
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2338,7 +2484,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFEDEDED"/>
@@ -2564,7 +2710,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -2607,37 +2753,48 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2645,35 +2802,35 @@
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -2693,10 +2850,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B9,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B9))</f>
@@ -2741,10 +2898,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B10,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B10))</f>
@@ -2789,10 +2946,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D11" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B11,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B11))</f>
@@ -2837,10 +2994,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B12,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B12))</f>
@@ -2885,10 +3042,10 @@
         <v>5</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D13" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B13,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B13))</f>
@@ -2927,7 +3084,7 @@
         <v>100</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2935,10 +3092,10 @@
         <v>6</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D14" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B14,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B14))</f>
@@ -2983,10 +3140,10 @@
         <v>7</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D15" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B15,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B15))</f>
@@ -3031,10 +3188,10 @@
         <v>8</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D16" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B16,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B16))</f>
@@ -3079,10 +3236,10 @@
         <v>9</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D17" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B17,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B17))</f>
@@ -3127,10 +3284,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D18" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B18,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B18))</f>
@@ -3175,10 +3332,10 @@
         <v>11</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D19" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B19,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B19))</f>
@@ -3223,10 +3380,10 @@
         <v>12</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D20" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B20,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B20))</f>
@@ -3271,10 +3428,10 @@
         <v>13</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D21" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B21,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B21))</f>
@@ -3319,10 +3476,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D22" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B22,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B22))</f>
@@ -3367,10 +3524,10 @@
         <v>15</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D23" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B23,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B23))</f>
@@ -3415,10 +3572,10 @@
         <v>16</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D24" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B24,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B24))</f>
@@ -3463,10 +3620,10 @@
         <v>17</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D25" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B25,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B25))</f>
@@ -3511,10 +3668,10 @@
         <v>18</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D26" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B26,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B26))</f>
@@ -3559,10 +3716,10 @@
         <v>19</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D27" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B27,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B27))</f>
@@ -3601,7 +3758,7 @@
         <v>1.9</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3609,10 +3766,10 @@
         <v>20</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D28" s="9" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B28,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B28))</f>
@@ -3651,18 +3808,18 @@
         <v>111000</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
         <v>21</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D29" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B29,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B29))</f>
@@ -3701,12 +3858,12 @@
         <v>295.6</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -3726,10 +3883,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D32" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B32,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B32))</f>
@@ -3774,10 +3931,10 @@
         <v>2</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D33" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B33,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B33))</f>
@@ -3822,10 +3979,10 @@
         <v>3</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D34" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B34,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B34))</f>
@@ -3870,10 +4027,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D35" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B35,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B35))</f>
@@ -3918,10 +4075,10 @@
         <v>5</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D36" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B36,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B36))</f>
@@ -3966,10 +4123,10 @@
         <v>6</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D37" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B37,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B37))</f>
@@ -4014,10 +4171,10 @@
         <v>7</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D38" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B38,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B38))</f>
@@ -4062,10 +4219,10 @@
         <v>8</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D39" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B39,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B39))</f>
@@ -4110,10 +4267,10 @@
         <v>9</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D40" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B40,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B40))</f>
@@ -4158,10 +4315,10 @@
         <v>10</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D41" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B41,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B41))</f>
@@ -4206,10 +4363,10 @@
         <v>11</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D42" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B42,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B42))</f>
@@ -4254,10 +4411,10 @@
         <v>12</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D43" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B43,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B43))</f>
@@ -4297,15 +4454,15 @@
       </c>
       <c r="M43" s="8"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
         <v>13</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D44" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B44,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B44))</f>
@@ -4315,25 +4472,25 @@
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B44,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B44))</f>
         <v/>
       </c>
-      <c r="F44" s="9" t="str">
+      <c r="F44" s="9" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B44,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B44))</f>
-        <v/>
+        <v>75.6</v>
       </c>
       <c r="G44" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B44,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B44))</f>
         <v/>
       </c>
-      <c r="H44" s="9" t="str">
+      <c r="H44" s="9" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B44,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B44))</f>
-        <v/>
+        <v>94.5</v>
       </c>
       <c r="I44" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B44,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B44))</f>
         <v/>
       </c>
-      <c r="J44" s="9" t="str">
+      <c r="J44" s="9" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B44,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B44))</f>
-        <v/>
+        <v>94.5</v>
       </c>
       <c r="K44" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B44,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B44))</f>
@@ -4343,17 +4500,19 @@
         <f aca="false">SUM(E44,G44,I44,K44)</f>
         <v>0</v>
       </c>
-      <c r="M44" s="8"/>
+      <c r="M44" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
         <v>14</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D45" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B45,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B45))</f>
@@ -4398,10 +4557,10 @@
         <v>15</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D46" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B46,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B46))</f>
@@ -4446,10 +4605,10 @@
         <v>16</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D47" s="9" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B47,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B47))</f>
@@ -4488,6 +4647,54 @@
         <v>0</v>
       </c>
       <c r="M47" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="9" t="str">
+        <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B48,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B48))</f>
+        <v/>
+      </c>
+      <c r="E48" s="9" t="str">
+        <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B48,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B48))</f>
+        <v/>
+      </c>
+      <c r="F48" s="9" t="str">
+        <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B48,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B48))</f>
+        <v/>
+      </c>
+      <c r="G48" s="9" t="str">
+        <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B48,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B48))</f>
+        <v/>
+      </c>
+      <c r="H48" s="9" t="str">
+        <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B48,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B48))</f>
+        <v/>
+      </c>
+      <c r="I48" s="9" t="str">
+        <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B48,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B48))</f>
+        <v/>
+      </c>
+      <c r="J48" s="9" t="str">
+        <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B48,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B48))</f>
+        <v/>
+      </c>
+      <c r="K48" s="9" t="str">
+        <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B48,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B48))</f>
+        <v/>
+      </c>
+      <c r="L48" s="10" t="n">
+        <f aca="false">SUM(E48,G48,I48,K48)</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -4532,48 +4739,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>63</v>
+      <c r="A2" s="12" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>64</v>
+      <c r="A3" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -4588,24 +4795,24 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E7" s="13"/>
       <c r="F7" s="9" t="n">
         <f aca="false">8*'통합 청구'!$C$3</f>
         <v>160</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4613,24 +4820,24 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E8" s="13"/>
       <c r="F8" s="9" t="n">
         <f aca="false">6*'통합 청구'!$C$3</f>
         <v>120</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4638,23 +4845,23 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="13"/>
+      <c r="F9" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13" t="n">
-        <v>108</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4662,24 +4869,24 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E10" s="13"/>
       <c r="F10" s="9" t="n">
         <f aca="false">9*'통합 청구'!$C$3</f>
         <v>180</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4687,23 +4894,23 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="13" t="n">
-        <v>108</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="H11" s="8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4711,24 +4918,24 @@
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E12" s="13"/>
       <c r="F12" s="9" t="n">
         <f aca="false">2*'통합 청구'!$C$3</f>
         <v>40</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4736,23 +4943,23 @@
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" s="13"/>
+      <c r="F13" s="14" t="n">
         <v>40</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4760,21 +4967,21 @@
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E14" s="13"/>
       <c r="F14" s="9" t="n">
         <f aca="false">2*'통합 청구'!$C$3</f>
         <v>40</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H14" s="8"/>
     </row>
@@ -4783,24 +4990,24 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="E15" s="13"/>
       <c r="F15" s="9" t="n">
         <f aca="false">3*'통합 청구'!$C$4</f>
         <v>54</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4808,31 +5015,31 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E16" s="14" t="n">
         <f aca="false">21250+740+3690</f>
         <v>25680</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="14" t="n">
         <v>21000</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -4847,16 +5054,16 @@
         <v>1</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
@@ -4865,16 +5072,16 @@
         <v>2</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
@@ -4883,16 +5090,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
@@ -4901,16 +5108,16 @@
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
@@ -4919,16 +5126,16 @@
         <v>5</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
     </row>
@@ -4937,16 +5144,16 @@
         <v>6</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
     </row>
@@ -4955,16 +5162,16 @@
         <v>7</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
@@ -4973,16 +5180,16 @@
         <v>8</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
     </row>
@@ -4991,16 +5198,16 @@
         <v>9</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
     </row>
@@ -5009,19 +5216,19 @@
         <v>10</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5029,19 +5236,19 @@
         <v>11</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5049,19 +5256,19 @@
         <v>12</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5069,16 +5276,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
@@ -5087,16 +5294,16 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
@@ -5105,16 +5312,16 @@
         <v>15</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
@@ -5123,16 +5330,16 @@
         <v>16</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
@@ -5141,19 +5348,19 @@
         <v>17</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="47.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5161,16 +5368,16 @@
         <v>18</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
@@ -5179,19 +5386,19 @@
         <v>19</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
       <c r="G36" s="8"/>
       <c r="H36" s="8" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5199,19 +5406,19 @@
         <v>20</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5219,16 +5426,16 @@
         <v>21</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
     </row>
@@ -5266,48 +5473,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>120</v>
+      <c r="A2" s="12" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>64</v>
+      <c r="A3" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -5322,20 +5529,20 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" s="14" t="n">
         <v>106</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="14" t="n">
         <v>200</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H7" s="8"/>
     </row>
@@ -5344,20 +5551,20 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <v>300</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H8" s="8"/>
     </row>
@@ -5366,20 +5573,20 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="14" t="n">
         <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H9" s="8"/>
     </row>
@@ -5388,23 +5595,23 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E10" s="14" t="n">
         <v>25080</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="14" t="n">
         <v>30000</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5412,30 +5619,30 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E11" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="14" t="n">
         <v>100</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>129</v>
+        <v>132</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -5445,23 +5652,33 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <f aca="false">4*'통합 청구'!$C$5</f>
+        <v>75.6</v>
+      </c>
+      <c r="F13" s="13"/>
+      <c r="G13" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>136</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="B13:H13"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5492,48 +5709,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>133</v>
+      <c r="A2" s="12" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>64</v>
+      <c r="A3" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -5548,20 +5765,20 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="14" t="n">
         <v>120</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H7" s="8"/>
     </row>
@@ -5570,25 +5787,25 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <v>40</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5596,25 +5813,25 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="14" t="n">
         <v>72</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5622,25 +5839,25 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" s="14" t="n">
         <v>52</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="14" t="n">
         <v>90</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5648,25 +5865,25 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E11" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="14" t="n">
         <v>20</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5674,20 +5891,20 @@
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="14" t="n">
         <v>40</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H12" s="8"/>
     </row>
@@ -5696,25 +5913,25 @@
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" s="14" t="n">
         <v>1400</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="14" t="n">
         <v>400</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5722,20 +5939,20 @@
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="14" t="n">
         <v>15000</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H14" s="8"/>
     </row>
@@ -5744,30 +5961,30 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E15" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="14" t="n">
         <v>120</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -5777,23 +5994,33 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <f aca="false">5*'통합 청구'!$C$5</f>
+        <v>94.5</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="G17" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>136</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="B17:H17"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5824,48 +6051,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>153</v>
+      <c r="A2" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>64</v>
+      <c r="A3" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -5880,24 +6107,24 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" s="14" t="n">
         <v>140</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="14" t="n">
         <f aca="false">3*18</f>
         <v>54</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5905,24 +6132,24 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <f aca="false">2*18</f>
         <v>36</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5930,23 +6157,23 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="14" t="n">
         <v>100</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5954,24 +6181,24 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="14" t="n">
         <f aca="false">10*18</f>
         <v>180</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5979,23 +6206,23 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E11" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="14" t="n">
         <v>160</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6003,23 +6230,23 @@
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E12" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="14" t="n">
         <v>100</v>
       </c>
       <c r="G12" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6027,23 +6254,23 @@
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="14" t="n">
         <v>60</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6051,23 +6278,23 @@
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E14" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="14" t="n">
         <v>60</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6075,23 +6302,23 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E15" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="14" t="n">
         <v>20</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6099,23 +6326,23 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E16" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="14" t="n">
         <v>18</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6123,24 +6350,24 @@
         <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" s="14" t="n">
         <v>102</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="14" t="n">
         <f aca="false">5*18</f>
         <v>90</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6148,24 +6375,24 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="14" t="n">
         <f aca="false">0.38*5</f>
         <v>1.9</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6173,20 +6400,20 @@
         <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E19" s="14" t="n">
         <v>19500</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="14" t="n">
         <v>45000</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H19" s="8"/>
     </row>
@@ -6195,31 +6422,31 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E20" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F20" s="14" t="n">
         <f aca="false">4*18.9</f>
         <v>75.6</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -6229,23 +6456,33 @@
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <f aca="false">5*'통합 청구'!$C$5</f>
+        <v>94.5</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>136</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="B22:H22"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/out/North_Fleet_Lub_Oil_Requisition.xlsx
+++ b/out/North_Fleet_Lub_Oil_Requisition.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="176">
   <si>
     <r>
       <rPr>
@@ -472,6 +472,40 @@
     <t xml:space="preserve">Item (Lub Oil / Grease)</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Purpose (</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용도</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Unit</t>
   </si>
   <si>
@@ -532,21 +566,147 @@
     <t xml:space="preserve">BARELF CH 100</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메인 공기압축기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Main air comp.)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">L</t>
   </si>
   <si>
     <t xml:space="preserve">BARELF SM 46</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서비스 공기압축기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Control·Service air comp.)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">BIOADHESIVE PLUS</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조타기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Steering gear), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비상예인장치 그리스</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">KG</t>
   </si>
   <si>
     <t xml:space="preserve">BIOMULTIS EP 0</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용도 확인 필요 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(North Light </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목록에 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">BSE 170</t>
   </si>
   <si>
@@ -556,30 +716,401 @@
     <t xml:space="preserve">CARTER SH 150</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">윈들러스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">윈치 기어박스 오일</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">CERAN AD PLUS</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">갑판기기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보일러</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">크레인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이빗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사다리 등 그리스</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">CERAN XM 220</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">갑판기기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">크레인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이빗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">캡스턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사다리 등 그리스</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">DACNIS 46</t>
   </si>
   <si>
     <t xml:space="preserve">DACNIS 100</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메인 공기압축기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Main air comp.) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">윤활유</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">ELFMATIC G3</t>
   </si>
   <si>
+    <t xml:space="preserve">구명정 데이빗 기어박스 오일</t>
+  </si>
+  <si>
     <t xml:space="preserve">EPONA SA 220</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GE LO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">청정기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Purifier), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">갑판장비 기어박스 겸용</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">EPONA Z 220</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">갑판 기어박스 오일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">크레인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이빗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">캡스턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사다리 릴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구명정</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">EPONA Z 460</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">발전기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(GE) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">터닝기어 오일</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">MULTIS COMPLEX SHD 100</t>
   </si>
   <si>
@@ -589,12 +1120,69 @@
     <t xml:space="preserve">MULTIS EP 2</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">범용 그리스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(General purpose)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">PRESLIA 100</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BOG </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부스트 컴프레서 크랭크케이스</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">SHELL GADUS S5 V42P 2.5</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">컴프레서 모터 그리스</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Valley: 5 tube × 380g</t>
   </si>
   <si>
@@ -608,7 +1196,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">M/E CYLINDER OIL. Light ROB = 3</t>
+      <t xml:space="preserve">M/E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실린더 오일</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Light ROB = 3</t>
     </r>
     <r>
       <rPr>
@@ -626,11 +1233,30 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Gardner Denver AEON 9000 / NITROGEN COMPRESSOR (Valley: </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">질소 압축기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Nitrogen comp.)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Gardner Denver AEON 9000 (Valley: </t>
     </r>
     <r>
       <rPr>
@@ -762,39 +1388,428 @@
     <t xml:space="preserve">ATLANTA MARINE D 3005</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선미관</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Stern tube) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">베어링</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">씰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중간축 베어링</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, M/E</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">AZOLLA AF 46</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">컴프레서 유압유</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">BIOMULTIS EP 2</t>
   </si>
   <si>
+    <t xml:space="preserve">프로펠러 캡 그리스</t>
+  </si>
+  <si>
     <t xml:space="preserve">DISOLA M 4015</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">발전기 엔진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(G/E) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">윤활유</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">DISOLA W 15W40</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비상발전기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구명정 엔진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비상예인장치</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">KOBELCO KL-435-46</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FG </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">컴프레서 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I/II (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">베어링</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">LOCTITE 8104</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">컴프레서 조립용 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Helkel </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">LOCTITE 8150</t>
   </si>
   <si>
     <t xml:space="preserve">PLANETELF ACD 46</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식료품 냉동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Prov. ref.) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">플랜트</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">PLANETELF ACD 68</t>
   </si>
   <si>
+    <t xml:space="preserve">거주구 에어컨 플랜트</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRESLIA 32</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FG </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">컴프레서 메인모터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유닛</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">PRESLIA 68</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조타기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">워터스프레이펌프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보일러 순환펌프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(EGE)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">TMC MARINE COMPRESSOR LUBE PLUS (P/N 301020)</t>
   </si>
   <si>
@@ -845,15 +1860,226 @@
     <t xml:space="preserve">VISGA 15</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">워터드레인펌프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">밸브 원격제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메인엔진</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">VISGA 32</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">갑판기기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·ME </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유압 톱브레이싱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">밸브 로컬컨트롤</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">VISGA 46</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">크레인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">호스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식료품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카고컴프레서룸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비상예인장치</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">VISGA 68</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HFO / ME LO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">청정기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Purifier)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">NORTH LIGHT – LUB OIL REQUISITION</t>
   </si>
   <si>
@@ -1110,7 +2336,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">' C3/C4 </t>
+      <t xml:space="preserve">' D3~D5 </t>
     </r>
     <r>
       <rPr>
@@ -1219,9 +2445,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Equipment / Use</t>
-  </si>
-  <si>
     <t xml:space="preserve">Original entry</t>
   </si>
   <si>
@@ -1246,108 +2469,45 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Main air compressor</t>
-  </si>
-  <si>
     <t xml:space="preserve">8 CAN</t>
   </si>
   <si>
     <t xml:space="preserve">1 can/month</t>
   </si>
   <si>
-    <t xml:space="preserve">Control/Service air compressor</t>
-  </si>
-  <si>
     <t xml:space="preserve">6 CAN</t>
   </si>
   <si>
     <t xml:space="preserve">40 ltr/set</t>
   </si>
   <si>
-    <t xml:space="preserve">STEERING GEAR, EMERGENCY TOWING SYSTEM &amp; ESCORTING PULL BACK SYSTEM</t>
-  </si>
-  <si>
     <t xml:space="preserve">108 KG (6 CAN)</t>
   </si>
   <si>
-    <t xml:space="preserve">windlass/winch gear box gear oil</t>
-  </si>
-  <si>
     <t xml:space="preserve">9 CAN</t>
   </si>
   <si>
     <t xml:space="preserve">each gear box 30~35ltr</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DECK MACHINERY, HOSE HANDLING CRANE, PROVISION CRANE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">외 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">life boat davit gear box oil</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 CAN</t>
   </si>
   <si>
     <t xml:space="preserve">Nil</t>
   </si>
   <si>
-    <t xml:space="preserve">GE LO PURIFIER</t>
-  </si>
-  <si>
     <t xml:space="preserve">40 L (20L/CAN)</t>
   </si>
   <si>
     <t xml:space="preserve">FOR DECK EQUIPMENTS GEAR BOX OIL</t>
   </si>
   <si>
-    <t xml:space="preserve">GE turning gear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General propose</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 CAN</t>
   </si>
   <si>
     <t xml:space="preserve">0.5 can/month</t>
   </si>
   <si>
-    <t xml:space="preserve">MAIN ENGINE</t>
-  </si>
-  <si>
     <t xml:space="preserve">21000 L</t>
   </si>
   <si>
@@ -1427,246 +2587,21 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">STERN TUBE BEARING AND SEAL, MAIN ENGINE, INTERMEDIATE SHAFT BEARING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VR COMPRESSOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROPELLER CAP</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DECK MACHINERY, AUX. BOILER, EGE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">외 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">MAIN AIR COMPRESSOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENERATOR ENGINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMERGENCY GENERATOR, LIFE/RESCUE BOAT WITH ENGINE, EMERGENCY TOWING SYSTEM &amp;</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LIFE/RESCUE BOAT WITH ENGINE, DECK MACHINERY, EMERGENCY TOWING SYSTEM &amp; ESCORTING PULL BACK SYSTEM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">외 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">FG COMPRESSOR I &amp; FG COMPRESSOR II, FG COMPRESSOR I, FG COMPRESSOR II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VR COMPRESSOR ASSEMBLY</t>
-  </si>
-  <si>
     <t xml:space="preserve">PURCHASED AT HELKEL.</t>
   </si>
   <si>
-    <t xml:space="preserve">PROV. REF. PLANT</t>
-  </si>
-  <si>
     <t xml:space="preserve">FIRST CHANGE : ABT. 100~ 200 HOURS</t>
   </si>
   <si>
-    <t xml:space="preserve">AIR-CON. PLANT FOR ACCOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAIN MOTOR LO UNIT FOR FGC I, MAIN MOTOR LO UNIT FOR FGC II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEERING GEAR, WATER SPRAY PUMP, NO.1~NO.4 BOILER WATER CIRC. PUMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOG BOOST COMPRESSOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VR COMPRESSOR MOTOR</t>
-  </si>
-  <si>
     <t xml:space="preserve">OIL SUPPLIER: SHELL OIL SUPPLIER : MOBIL OIL SUPPLIER : SKF</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WATER DRAIN PUMP FOR SECONDARY, WATER DRAIN PUMP FOR GLYCOL WATER, WATER DRAIN PUMP FOR OILY BILGE FOR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">외 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DECK MACHINERY, LATHE MACHINE, ME HYD. TOP BRACHING </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">외 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">INITIALLY FILLED BY MAKER BUT SHOULD BE REPLACED BEFORE SEA TRIALL; INITIALLY FILLED BY MAKER BUT SHOULD BE REPLACED BEFORE SEA TRIAL; INITIALLY FILLED BY MAKER BUT SHOULD BE REPLACED BEFORE SEA TRIAL; CHANGED FROM RANDO HDZ 22 TO HDZ 32 WITH MAKER, CHEVRON CONFIRMED</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HOSE HANDLING CRANE, PROVISION CRANE, CARGO COMPRESSOR ROOM AND ELEC. ROOM CRANE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">외 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">INITIALLY FILLED BY MAKER BUT SHULD BE REPLACED BEFORE SEA TRIAL</t>
   </si>
   <si>
-    <t xml:space="preserve">HFO PURIFIER, ME LO PURIFIER</t>
-  </si>
-  <si>
     <t xml:space="preserve">NORTH MOON – LUB OIL REQUISITION</t>
   </si>
   <si>
@@ -1782,9 +2717,6 @@
     <t xml:space="preserve">M/E CYLINDER OIL</t>
   </si>
   <si>
-    <t xml:space="preserve">NITROGEN COMPRESSOR</t>
-  </si>
-  <si>
     <t xml:space="preserve">100 Liters</t>
   </si>
   <si>
@@ -1906,6 +2838,42 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용도 확인 필요 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(North Light </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목록에 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">4 PAILS (75.6 LT)</t>
   </si>
   <si>
@@ -2053,15 +3021,9 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">GS AND CONTROL AIR COMPRESSOR</t>
-  </si>
-  <si>
     <t xml:space="preserve">120 L</t>
   </si>
   <si>
-    <t xml:space="preserve">DECK MACHINERY</t>
-  </si>
-  <si>
     <t xml:space="preserve">40 L</t>
   </si>
   <si>
@@ -2084,12 +3046,6 @@
   </si>
   <si>
     <t xml:space="preserve">ROB: 48 ltrs.  Multipurpose oil for purifiers and deck equipment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWS DIESEL GENERATOR TURNING GEAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOG BOOST COMPRESSOR (CRANK CASE)</t>
   </si>
   <si>
     <t xml:space="preserve">400 L</t>
@@ -2218,7 +3174,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[=0]\-;[&gt;=1000]#,##0;General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2298,10 +3254,22 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2311,9 +3279,19 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
       <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2397,7 +3375,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2426,15 +3404,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2442,7 +3424,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2450,7 +3432,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2484,7 +3466,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFEDEDED"/>
@@ -2710,15 +3692,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="5" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2735,10 +3718,10 @@
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="D3" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2746,10 +3729,10 @@
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="D4" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2757,10 +3740,10 @@
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2777,60 +3760,64 @@
       <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
+      <c r="H6" s="5"/>
+      <c r="I6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
+      <c r="J6" s="5"/>
+      <c r="K6" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
         <v>16</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-      <c r="D7" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="5"/>
+      <c r="L7" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -2844,247 +3831,263 @@
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="9" t="str">
+      <c r="C9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B9,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B9))</f>
         <v/>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B9,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B9))</f>
         <v>160</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B9,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B9))</f>
         <v>106</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="H9" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B9,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B9))</f>
         <v>200</v>
       </c>
-      <c r="H9" s="9" t="str">
+      <c r="I9" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B9,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B9))</f>
         <v/>
       </c>
-      <c r="I9" s="9" t="str">
+      <c r="J9" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B9,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B9))</f>
         <v/>
       </c>
-      <c r="J9" s="9" t="str">
+      <c r="K9" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B9,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B9))</f>
         <v/>
       </c>
-      <c r="K9" s="9" t="str">
+      <c r="L9" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B9,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B9))</f>
         <v/>
       </c>
-      <c r="L9" s="10" t="n">
-        <f aca="false">SUM(E9,G9,I9,K9)</f>
+      <c r="M9" s="11" t="n">
+        <f aca="false">SUM(F9,H9,J9,L9)</f>
         <v>360</v>
       </c>
-      <c r="M9" s="8"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
         <v>2</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="9" t="str">
+        <v>24</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B10,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B10))</f>
         <v/>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B10,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B10))</f>
         <v>120</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="G10" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B10,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B10))</f>
         <v>120</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="H10" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B10,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B10))</f>
         <v>300</v>
       </c>
-      <c r="H10" s="9" t="str">
+      <c r="I10" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B10,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B10))</f>
         <v/>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="J10" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B10,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B10))</f>
         <v>120</v>
       </c>
-      <c r="J10" s="9" t="str">
+      <c r="K10" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B10,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B10))</f>
         <v/>
       </c>
-      <c r="K10" s="9" t="str">
+      <c r="L10" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B10,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B10))</f>
         <v/>
       </c>
-      <c r="L10" s="10" t="n">
-        <f aca="false">SUM(E10,G10,I10,K10)</f>
+      <c r="M10" s="11" t="n">
+        <f aca="false">SUM(F10,H10,J10,L10)</f>
         <v>540</v>
       </c>
-      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
         <v>3</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="9" t="str">
+        <v>26</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B11,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B11))</f>
         <v/>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B11,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B11))</f>
         <v>108</v>
       </c>
-      <c r="F11" s="9" t="str">
+      <c r="G11" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B11,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B11))</f>
         <v/>
       </c>
-      <c r="G11" s="9" t="str">
+      <c r="H11" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B11,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B11))</f>
         <v/>
       </c>
-      <c r="H11" s="9" t="str">
+      <c r="I11" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B11,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B11))</f>
         <v/>
       </c>
-      <c r="I11" s="9" t="str">
+      <c r="J11" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B11,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B11))</f>
         <v/>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="K11" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B11,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B11))</f>
         <v>140</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="L11" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B11,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B11))</f>
         <v>54</v>
       </c>
-      <c r="L11" s="10" t="n">
-        <f aca="false">SUM(E11,G11,I11,K11)</f>
+      <c r="M11" s="11" t="n">
+        <f aca="false">SUM(F11,H11,J11,L11)</f>
         <v>162</v>
       </c>
-      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="9" t="str">
+        <v>29</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B12,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B12))</f>
         <v/>
       </c>
-      <c r="E12" s="9" t="str">
+      <c r="F12" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B12,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B12))</f>
         <v/>
       </c>
-      <c r="F12" s="9" t="str">
+      <c r="G12" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B12,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B12))</f>
         <v/>
       </c>
-      <c r="G12" s="9" t="str">
+      <c r="H12" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B12,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B12))</f>
         <v/>
       </c>
-      <c r="H12" s="9" t="str">
+      <c r="I12" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B12,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B12))</f>
         <v/>
       </c>
-      <c r="I12" s="9" t="str">
+      <c r="J12" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B12,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B12))</f>
         <v/>
       </c>
-      <c r="J12" s="9" t="n">
+      <c r="K12" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B12,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B12))</f>
         <v>36</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="L12" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B12,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B12))</f>
         <v>36</v>
       </c>
-      <c r="L12" s="10" t="n">
-        <f aca="false">SUM(E12,G12,I12,K12)</f>
+      <c r="M12" s="11" t="n">
+        <f aca="false">SUM(F12,H12,J12,L12)</f>
         <v>36</v>
       </c>
-      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
         <v>5</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="9" t="str">
+        <v>31</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B13,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B13))</f>
         <v/>
       </c>
-      <c r="E13" s="9" t="str">
+      <c r="F13" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B13,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B13))</f>
         <v/>
       </c>
-      <c r="F13" s="9" t="str">
+      <c r="G13" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B13,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B13))</f>
         <v/>
       </c>
-      <c r="G13" s="9" t="str">
+      <c r="H13" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B13,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B13))</f>
         <v/>
       </c>
-      <c r="H13" s="9" t="str">
+      <c r="I13" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B13,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B13))</f>
         <v/>
       </c>
-      <c r="I13" s="9" t="str">
+      <c r="J13" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B13,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B13))</f>
         <v/>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="K13" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B13,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B13))</f>
         <v>130</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="L13" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B13,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B13))</f>
         <v>100</v>
       </c>
-      <c r="L13" s="10" t="n">
-        <f aca="false">SUM(E13,G13,I13,K13)</f>
+      <c r="M13" s="11" t="n">
+        <f aca="false">SUM(F13,H13,J13,L13)</f>
         <v>100</v>
       </c>
-      <c r="M13" s="8" t="s">
-        <v>27</v>
+      <c r="N13" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3092,673 +4095,715 @@
         <v>6</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="9" t="str">
+        <v>33</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B14,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B14))</f>
         <v/>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="F14" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B14,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B14))</f>
         <v>180</v>
       </c>
-      <c r="F14" s="9" t="str">
+      <c r="G14" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B14,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B14))</f>
         <v/>
       </c>
-      <c r="G14" s="9" t="str">
+      <c r="H14" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B14,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B14))</f>
         <v/>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="I14" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B14,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B14))</f>
         <v>27</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="J14" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B14,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B14))</f>
         <v>40</v>
       </c>
-      <c r="J14" s="9" t="str">
+      <c r="K14" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B14,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B14))</f>
         <v/>
       </c>
-      <c r="K14" s="9" t="str">
+      <c r="L14" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B14,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B14))</f>
         <v/>
       </c>
-      <c r="L14" s="10" t="n">
-        <f aca="false">SUM(E14,G14,I14,K14)</f>
+      <c r="M14" s="11" t="n">
+        <f aca="false">SUM(F14,H14,J14,L14)</f>
         <v>220</v>
       </c>
-      <c r="M14" s="8"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N14" s="8"/>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
         <v>7</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="9" t="str">
+        <v>35</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B15,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B15))</f>
         <v/>
       </c>
-      <c r="E15" s="9" t="str">
+      <c r="F15" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B15,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B15))</f>
         <v/>
       </c>
-      <c r="F15" s="9" t="str">
+      <c r="G15" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B15,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B15))</f>
         <v/>
       </c>
-      <c r="G15" s="9" t="str">
+      <c r="H15" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B15,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B15))</f>
         <v/>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="I15" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B15,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B15))</f>
         <v>27</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="J15" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B15,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B15))</f>
         <v>72</v>
       </c>
-      <c r="J15" s="9" t="str">
+      <c r="K15" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B15,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B15))</f>
         <v/>
       </c>
-      <c r="K15" s="9" t="str">
+      <c r="L15" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B15,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B15))</f>
         <v/>
       </c>
-      <c r="L15" s="10" t="n">
-        <f aca="false">SUM(E15,G15,I15,K15)</f>
+      <c r="M15" s="11" t="n">
+        <f aca="false">SUM(F15,H15,J15,L15)</f>
         <v>72</v>
       </c>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N15" s="8"/>
+    </row>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
         <v>8</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="9" t="str">
+        <v>37</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B16,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B16))</f>
         <v/>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="F16" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B16,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B16))</f>
         <v>108</v>
       </c>
-      <c r="F16" s="9" t="str">
+      <c r="G16" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B16,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B16))</f>
         <v/>
       </c>
-      <c r="G16" s="9" t="str">
+      <c r="H16" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B16,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B16))</f>
         <v/>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="I16" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B16,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B16))</f>
         <v>52</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="J16" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B16,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B16))</f>
         <v>90</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="K16" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B16,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B16))</f>
         <v>70</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="L16" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B16,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B16))</f>
         <v>180</v>
       </c>
-      <c r="L16" s="10" t="n">
-        <f aca="false">SUM(E16,G16,I16,K16)</f>
+      <c r="M16" s="11" t="n">
+        <f aca="false">SUM(F16,H16,J16,L16)</f>
         <v>378</v>
       </c>
-      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
         <v>9</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="9" t="str">
+        <v>39</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B17,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B17))</f>
         <v/>
       </c>
-      <c r="E17" s="9" t="str">
+      <c r="F17" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B17,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B17))</f>
         <v/>
       </c>
-      <c r="F17" s="9" t="str">
+      <c r="G17" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B17,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B17))</f>
         <v/>
       </c>
-      <c r="G17" s="9" t="str">
+      <c r="H17" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B17,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B17))</f>
         <v/>
       </c>
-      <c r="H17" s="9" t="str">
+      <c r="I17" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B17,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B17))</f>
         <v/>
       </c>
-      <c r="I17" s="9" t="str">
+      <c r="J17" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B17,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B17))</f>
         <v/>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="K17" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B17,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B17))</f>
         <v>40</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="L17" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B17,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B17))</f>
         <v>160</v>
       </c>
-      <c r="L17" s="10" t="n">
-        <f aca="false">SUM(E17,G17,I17,K17)</f>
+      <c r="M17" s="11" t="n">
+        <f aca="false">SUM(F17,H17,J17,L17)</f>
         <v>160</v>
       </c>
-      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
         <v>10</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="9" t="str">
+        <v>40</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B18,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B18))</f>
         <v/>
       </c>
-      <c r="E18" s="9" t="str">
+      <c r="F18" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B18,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B18))</f>
         <v/>
       </c>
-      <c r="F18" s="9" t="str">
+      <c r="G18" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B18,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B18))</f>
         <v/>
       </c>
-      <c r="G18" s="9" t="str">
+      <c r="H18" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B18,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B18))</f>
         <v/>
       </c>
-      <c r="H18" s="9" t="str">
+      <c r="I18" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B18,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B18))</f>
         <v/>
       </c>
-      <c r="I18" s="9" t="str">
+      <c r="J18" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B18,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B18))</f>
         <v/>
       </c>
-      <c r="J18" s="9" t="n">
+      <c r="K18" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B18,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B18))</f>
         <v>150</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="L18" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B18,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B18))</f>
         <v>100</v>
       </c>
-      <c r="L18" s="10" t="n">
-        <f aca="false">SUM(E18,G18,I18,K18)</f>
+      <c r="M18" s="11" t="n">
+        <f aca="false">SUM(F18,H18,J18,L18)</f>
         <v>100</v>
       </c>
-      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
         <v>11</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="9" t="str">
+        <v>42</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B19,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B19))</f>
         <v/>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="F19" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B19,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B19))</f>
         <v>40</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="G19" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B19,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B19))</f>
         <v>0</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="H19" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B19,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B19))</f>
         <v>20</v>
       </c>
-      <c r="H19" s="9" t="str">
+      <c r="I19" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B19,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B19))</f>
         <v/>
       </c>
-      <c r="I19" s="9" t="str">
+      <c r="J19" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B19,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B19))</f>
         <v/>
       </c>
-      <c r="J19" s="9" t="str">
+      <c r="K19" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B19,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B19))</f>
         <v/>
       </c>
-      <c r="K19" s="9" t="str">
+      <c r="L19" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B19,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B19))</f>
         <v/>
       </c>
-      <c r="L19" s="10" t="n">
-        <f aca="false">SUM(E19,G19,I19,K19)</f>
+      <c r="M19" s="11" t="n">
+        <f aca="false">SUM(F19,H19,J19,L19)</f>
         <v>60</v>
       </c>
-      <c r="M19" s="8"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N19" s="8"/>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
         <v>12</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="9" t="str">
+        <v>44</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B20,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B20))</f>
         <v/>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="F20" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B20,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B20))</f>
         <v>40</v>
       </c>
-      <c r="F20" s="9" t="str">
+      <c r="G20" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B20,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B20))</f>
         <v/>
       </c>
-      <c r="G20" s="9" t="str">
+      <c r="H20" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B20,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B20))</f>
         <v/>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="I20" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B20,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B20))</f>
         <v>48</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="J20" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B20,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B20))</f>
         <v>20</v>
       </c>
-      <c r="J20" s="9" t="n">
+      <c r="K20" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B20,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B20))</f>
         <v>50</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="L20" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B20,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B20))</f>
         <v>60</v>
       </c>
-      <c r="L20" s="10" t="n">
-        <f aca="false">SUM(E20,G20,I20,K20)</f>
+      <c r="M20" s="11" t="n">
+        <f aca="false">SUM(F20,H20,J20,L20)</f>
         <v>120</v>
       </c>
-      <c r="M20" s="8"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N20" s="8"/>
+    </row>
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
         <v>13</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="9" t="str">
+        <v>46</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B21,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B21))</f>
         <v/>
       </c>
-      <c r="E21" s="9" t="str">
+      <c r="F21" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B21,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B21))</f>
         <v/>
       </c>
-      <c r="F21" s="9" t="str">
+      <c r="G21" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B21,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B21))</f>
         <v/>
       </c>
-      <c r="G21" s="9" t="str">
+      <c r="H21" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B21,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B21))</f>
         <v/>
       </c>
-      <c r="H21" s="9" t="str">
+      <c r="I21" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B21,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B21))</f>
         <v/>
       </c>
-      <c r="I21" s="9" t="str">
+      <c r="J21" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B21,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B21))</f>
         <v/>
       </c>
-      <c r="J21" s="9" t="n">
+      <c r="K21" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B21,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B21))</f>
         <v>80</v>
       </c>
-      <c r="K21" s="9" t="n">
+      <c r="L21" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B21,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B21))</f>
         <v>60</v>
       </c>
-      <c r="L21" s="10" t="n">
-        <f aca="false">SUM(E21,G21,I21,K21)</f>
+      <c r="M21" s="11" t="n">
+        <f aca="false">SUM(F21,H21,J21,L21)</f>
         <v>60</v>
       </c>
-      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
         <v>14</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="9" t="str">
+        <v>48</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B22,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B22))</f>
         <v/>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="F22" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B22,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B22))</f>
         <v>40</v>
       </c>
-      <c r="F22" s="9" t="str">
+      <c r="G22" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B22,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B22))</f>
         <v/>
       </c>
-      <c r="G22" s="9" t="str">
+      <c r="H22" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B22,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B22))</f>
         <v/>
       </c>
-      <c r="H22" s="9" t="str">
+      <c r="I22" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B22,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B22))</f>
         <v/>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="J22" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B22,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B22))</f>
         <v>40</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="K22" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B22,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B22))</f>
         <v>20</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="L22" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B22,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B22))</f>
         <v>20</v>
       </c>
-      <c r="L22" s="10" t="n">
-        <f aca="false">SUM(E22,G22,I22,K22)</f>
+      <c r="M22" s="11" t="n">
+        <f aca="false">SUM(F22,H22,J22,L22)</f>
         <v>100</v>
       </c>
-      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
         <v>15</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="9" t="str">
+        <v>50</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B23,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B23))</f>
         <v/>
       </c>
-      <c r="E23" s="9" t="str">
+      <c r="F23" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B23,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B23))</f>
         <v/>
       </c>
-      <c r="F23" s="9" t="str">
+      <c r="G23" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B23,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B23))</f>
         <v/>
       </c>
-      <c r="G23" s="9" t="str">
+      <c r="H23" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B23,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B23))</f>
         <v/>
       </c>
-      <c r="H23" s="9" t="str">
+      <c r="I23" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B23,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B23))</f>
         <v/>
       </c>
-      <c r="I23" s="9" t="str">
+      <c r="J23" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B23,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B23))</f>
         <v/>
       </c>
-      <c r="J23" s="9" t="n">
+      <c r="K23" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B23,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B23))</f>
         <v>0</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="L23" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B23,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B23))</f>
         <v>18</v>
       </c>
-      <c r="L23" s="10" t="n">
-        <f aca="false">SUM(E23,G23,I23,K23)</f>
+      <c r="M23" s="11" t="n">
+        <f aca="false">SUM(F23,H23,J23,L23)</f>
         <v>18</v>
       </c>
-      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
         <v>16</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="9" t="str">
+        <v>51</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B24,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B24))</f>
         <v/>
       </c>
-      <c r="E24" s="9" t="str">
+      <c r="F24" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B24,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B24))</f>
         <v/>
       </c>
-      <c r="F24" s="9" t="str">
+      <c r="G24" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B24,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B24))</f>
         <v/>
       </c>
-      <c r="G24" s="9" t="str">
+      <c r="H24" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B24,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B24))</f>
         <v/>
       </c>
-      <c r="H24" s="9" t="str">
+      <c r="I24" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B24,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B24))</f>
         <v/>
       </c>
-      <c r="I24" s="9" t="str">
+      <c r="J24" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B24,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B24))</f>
         <v/>
       </c>
-      <c r="J24" s="9" t="n">
+      <c r="K24" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B24,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B24))</f>
         <v>102</v>
       </c>
-      <c r="K24" s="9" t="n">
+      <c r="L24" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B24,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B24))</f>
         <v>90</v>
       </c>
-      <c r="L24" s="10" t="n">
-        <f aca="false">SUM(E24,G24,I24,K24)</f>
+      <c r="M24" s="11" t="n">
+        <f aca="false">SUM(F24,H24,J24,L24)</f>
         <v>90</v>
       </c>
-      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
         <v>17</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="9" t="str">
+        <v>52</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B25,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B25))</f>
         <v/>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B25,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B25))</f>
         <v>54</v>
       </c>
-      <c r="F25" s="9" t="str">
+      <c r="G25" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B25,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B25))</f>
         <v/>
       </c>
-      <c r="G25" s="9" t="str">
+      <c r="H25" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B25,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B25))</f>
         <v/>
       </c>
-      <c r="H25" s="9" t="str">
+      <c r="I25" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B25,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B25))</f>
         <v/>
       </c>
-      <c r="I25" s="9" t="str">
+      <c r="J25" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B25,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B25))</f>
         <v/>
       </c>
-      <c r="J25" s="9" t="str">
+      <c r="K25" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B25,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B25))</f>
         <v/>
       </c>
-      <c r="K25" s="9" t="str">
+      <c r="L25" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B25,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B25))</f>
         <v/>
       </c>
-      <c r="L25" s="10" t="n">
-        <f aca="false">SUM(E25,G25,I25,K25)</f>
+      <c r="M25" s="11" t="n">
+        <f aca="false">SUM(F25,H25,J25,L25)</f>
         <v>54</v>
       </c>
-      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
         <v>18</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="9" t="str">
+        <v>54</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B26,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B26))</f>
         <v/>
       </c>
-      <c r="E26" s="9" t="str">
+      <c r="F26" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B26,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B26))</f>
         <v/>
       </c>
-      <c r="F26" s="9" t="str">
+      <c r="G26" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B26,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B26))</f>
         <v/>
       </c>
-      <c r="G26" s="9" t="str">
+      <c r="H26" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B26,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B26))</f>
         <v/>
       </c>
-      <c r="H26" s="9" t="n">
+      <c r="I26" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B26,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B26))</f>
         <v>1400</v>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="J26" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B26,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B26))</f>
         <v>400</v>
       </c>
-      <c r="J26" s="9" t="str">
+      <c r="K26" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B26,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B26))</f>
         <v/>
       </c>
-      <c r="K26" s="9" t="str">
+      <c r="L26" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B26,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B26))</f>
         <v/>
       </c>
-      <c r="L26" s="10" t="n">
-        <f aca="false">SUM(E26,G26,I26,K26)</f>
+      <c r="M26" s="11" t="n">
+        <f aca="false">SUM(F26,H26,J26,L26)</f>
         <v>400</v>
       </c>
-      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
         <v>19</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="9" t="str">
+        <v>56</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B27,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B27))</f>
         <v/>
       </c>
-      <c r="E27" s="9" t="str">
+      <c r="F27" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B27,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B27))</f>
         <v/>
       </c>
-      <c r="F27" s="9" t="str">
+      <c r="G27" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B27,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B27))</f>
         <v/>
       </c>
-      <c r="G27" s="9" t="str">
+      <c r="H27" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B27,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B27))</f>
         <v/>
       </c>
-      <c r="H27" s="9" t="str">
+      <c r="I27" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B27,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B27))</f>
         <v/>
       </c>
-      <c r="I27" s="9" t="str">
+      <c r="J27" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B27,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B27))</f>
         <v/>
       </c>
-      <c r="J27" s="9" t="n">
+      <c r="K27" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B27,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B27))</f>
         <v>0</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="L27" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B27,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B27))</f>
         <v>1.9</v>
       </c>
-      <c r="L27" s="10" t="n">
-        <f aca="false">SUM(E27,G27,I27,K27)</f>
+      <c r="M27" s="11" t="n">
+        <f aca="false">SUM(F27,H27,J27,L27)</f>
         <v>1.9</v>
       </c>
-      <c r="M27" s="8" t="s">
-        <v>42</v>
+      <c r="N27" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3766,104 +4811,110 @@
         <v>20</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B28,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B28))</f>
         <v>25680</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="F28" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B28,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B28))</f>
         <v>21000</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="G28" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B28,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B28))</f>
         <v>25080</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="H28" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B28,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B28))</f>
         <v>30000</v>
       </c>
-      <c r="H28" s="9" t="str">
+      <c r="I28" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B28,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B28))</f>
         <v/>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="J28" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B28,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B28))</f>
         <v>15000</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="K28" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B28,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B28))</f>
         <v>19500</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="L28" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B28,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B28))</f>
         <v>45000</v>
       </c>
-      <c r="L28" s="10" t="n">
-        <f aca="false">SUM(E28,G28,I28,K28)</f>
+      <c r="M28" s="11" t="n">
+        <f aca="false">SUM(F28,H28,J28,L28)</f>
         <v>111000</v>
       </c>
-      <c r="M28" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N28" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
         <v>21</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="9" t="str">
+        <v>62</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B29,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B29))</f>
         <v/>
       </c>
-      <c r="E29" s="9" t="str">
+      <c r="F29" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B29,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B29))</f>
         <v/>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="G29" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B29,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B29))</f>
         <v>130</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="H29" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B29,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B29))</f>
         <v>100</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="I29" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B29,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B29))</f>
         <v>70</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="J29" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B29,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B29))</f>
         <v>120</v>
       </c>
-      <c r="J29" s="9" t="n">
+      <c r="K29" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B29,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B29))</f>
         <v>70</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="L29" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B29,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B29))</f>
         <v>75.6</v>
       </c>
-      <c r="L29" s="10" t="n">
-        <f aca="false">SUM(E29,G29,I29,K29)</f>
+      <c r="M29" s="11" t="n">
+        <f aca="false">SUM(F29,H29,J29,L29)</f>
         <v>295.6</v>
       </c>
-      <c r="M29" s="8" t="s">
-        <v>46</v>
+      <c r="N29" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -3877,631 +4928,671 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="9" t="str">
+        <v>66</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B32,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B32))</f>
         <v/>
       </c>
-      <c r="E32" s="9" t="str">
+      <c r="F32" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B32,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B32))</f>
         <v/>
       </c>
-      <c r="F32" s="9" t="str">
+      <c r="G32" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B32,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B32))</f>
         <v/>
       </c>
-      <c r="G32" s="9" t="str">
+      <c r="H32" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B32,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B32))</f>
         <v/>
       </c>
-      <c r="H32" s="9" t="str">
+      <c r="I32" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B32,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B32))</f>
         <v/>
       </c>
-      <c r="I32" s="9" t="str">
+      <c r="J32" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B32,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B32))</f>
         <v/>
       </c>
-      <c r="J32" s="9" t="str">
+      <c r="K32" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B32,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B32))</f>
         <v/>
       </c>
-      <c r="K32" s="9" t="str">
+      <c r="L32" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B32,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B32))</f>
         <v/>
       </c>
-      <c r="L32" s="10" t="n">
-        <f aca="false">SUM(E32,G32,I32,K32)</f>
+      <c r="M32" s="11" t="n">
+        <f aca="false">SUM(F32,H32,J32,L32)</f>
         <v>0</v>
       </c>
-      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
         <v>2</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="9" t="str">
+        <v>68</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B33,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B33))</f>
         <v/>
       </c>
-      <c r="E33" s="9" t="str">
+      <c r="F33" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B33,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B33))</f>
         <v/>
       </c>
-      <c r="F33" s="9" t="str">
+      <c r="G33" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B33,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B33))</f>
         <v/>
       </c>
-      <c r="G33" s="9" t="str">
+      <c r="H33" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B33,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B33))</f>
         <v/>
       </c>
-      <c r="H33" s="9" t="str">
+      <c r="I33" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B33,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B33))</f>
         <v/>
       </c>
-      <c r="I33" s="9" t="str">
+      <c r="J33" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B33,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B33))</f>
         <v/>
       </c>
-      <c r="J33" s="9" t="str">
+      <c r="K33" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B33,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B33))</f>
         <v/>
       </c>
-      <c r="K33" s="9" t="str">
+      <c r="L33" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B33,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B33))</f>
         <v/>
       </c>
-      <c r="L33" s="10" t="n">
-        <f aca="false">SUM(E33,G33,I33,K33)</f>
+      <c r="M33" s="11" t="n">
+        <f aca="false">SUM(F33,H33,J33,L33)</f>
         <v>0</v>
       </c>
-      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
         <v>3</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="9" t="str">
+        <v>70</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B34,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B34))</f>
         <v/>
       </c>
-      <c r="E34" s="9" t="str">
+      <c r="F34" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B34,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B34))</f>
         <v/>
       </c>
-      <c r="F34" s="9" t="str">
+      <c r="G34" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B34,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B34))</f>
         <v/>
       </c>
-      <c r="G34" s="9" t="str">
+      <c r="H34" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B34,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B34))</f>
         <v/>
       </c>
-      <c r="H34" s="9" t="str">
+      <c r="I34" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B34,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B34))</f>
         <v/>
       </c>
-      <c r="I34" s="9" t="str">
+      <c r="J34" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B34,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B34))</f>
         <v/>
       </c>
-      <c r="J34" s="9" t="str">
+      <c r="K34" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B34,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B34))</f>
         <v/>
       </c>
-      <c r="K34" s="9" t="str">
+      <c r="L34" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B34,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B34))</f>
         <v/>
       </c>
-      <c r="L34" s="10" t="n">
-        <f aca="false">SUM(E34,G34,I34,K34)</f>
+      <c r="M34" s="11" t="n">
+        <f aca="false">SUM(F34,H34,J34,L34)</f>
         <v>0</v>
       </c>
-      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="9" t="str">
+        <v>72</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B35,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B35))</f>
         <v/>
       </c>
-      <c r="E35" s="9" t="str">
+      <c r="F35" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B35,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B35))</f>
         <v/>
       </c>
-      <c r="F35" s="9" t="str">
+      <c r="G35" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B35,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B35))</f>
         <v/>
       </c>
-      <c r="G35" s="9" t="str">
+      <c r="H35" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B35,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B35))</f>
         <v/>
       </c>
-      <c r="H35" s="9" t="str">
+      <c r="I35" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B35,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B35))</f>
         <v/>
       </c>
-      <c r="I35" s="9" t="str">
+      <c r="J35" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B35,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B35))</f>
         <v/>
       </c>
-      <c r="J35" s="9" t="str">
+      <c r="K35" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B35,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B35))</f>
         <v/>
       </c>
-      <c r="K35" s="9" t="str">
+      <c r="L35" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B35,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B35))</f>
         <v/>
       </c>
-      <c r="L35" s="10" t="n">
-        <f aca="false">SUM(E35,G35,I35,K35)</f>
+      <c r="M35" s="11" t="n">
+        <f aca="false">SUM(F35,H35,J35,L35)</f>
         <v>0</v>
       </c>
-      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
         <v>5</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="9" t="str">
+        <v>74</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B36,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B36))</f>
         <v/>
       </c>
-      <c r="E36" s="9" t="str">
+      <c r="F36" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B36,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B36))</f>
         <v/>
       </c>
-      <c r="F36" s="9" t="str">
+      <c r="G36" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B36,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B36))</f>
         <v/>
       </c>
-      <c r="G36" s="9" t="str">
+      <c r="H36" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B36,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B36))</f>
         <v/>
       </c>
-      <c r="H36" s="9" t="str">
+      <c r="I36" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B36,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B36))</f>
         <v/>
       </c>
-      <c r="I36" s="9" t="str">
+      <c r="J36" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B36,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B36))</f>
         <v/>
       </c>
-      <c r="J36" s="9" t="str">
+      <c r="K36" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B36,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B36))</f>
         <v/>
       </c>
-      <c r="K36" s="9" t="str">
+      <c r="L36" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B36,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B36))</f>
         <v/>
       </c>
-      <c r="L36" s="10" t="n">
-        <f aca="false">SUM(E36,G36,I36,K36)</f>
+      <c r="M36" s="11" t="n">
+        <f aca="false">SUM(F36,H36,J36,L36)</f>
         <v>0</v>
       </c>
-      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="9" t="str">
+        <v>76</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B37,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B37))</f>
         <v/>
       </c>
-      <c r="E37" s="9" t="str">
+      <c r="F37" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B37,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B37))</f>
         <v/>
       </c>
-      <c r="F37" s="9" t="str">
+      <c r="G37" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B37,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B37))</f>
         <v/>
       </c>
-      <c r="G37" s="9" t="str">
+      <c r="H37" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B37,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B37))</f>
         <v/>
       </c>
-      <c r="H37" s="9" t="str">
+      <c r="I37" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B37,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B37))</f>
         <v/>
       </c>
-      <c r="I37" s="9" t="str">
+      <c r="J37" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B37,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B37))</f>
         <v/>
       </c>
-      <c r="J37" s="9" t="str">
+      <c r="K37" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B37,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B37))</f>
         <v/>
       </c>
-      <c r="K37" s="9" t="str">
+      <c r="L37" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B37,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B37))</f>
         <v/>
       </c>
-      <c r="L37" s="10" t="n">
-        <f aca="false">SUM(E37,G37,I37,K37)</f>
+      <c r="M37" s="11" t="n">
+        <f aca="false">SUM(F37,H37,J37,L37)</f>
         <v>0</v>
       </c>
-      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
         <v>7</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="9" t="str">
+        <v>78</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B38,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B38))</f>
         <v/>
       </c>
-      <c r="E38" s="9" t="str">
+      <c r="F38" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B38,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B38))</f>
         <v/>
       </c>
-      <c r="F38" s="9" t="str">
+      <c r="G38" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B38,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B38))</f>
         <v/>
       </c>
-      <c r="G38" s="9" t="str">
+      <c r="H38" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B38,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B38))</f>
         <v/>
       </c>
-      <c r="H38" s="9" t="str">
+      <c r="I38" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B38,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B38))</f>
         <v/>
       </c>
-      <c r="I38" s="9" t="str">
+      <c r="J38" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B38,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B38))</f>
         <v/>
       </c>
-      <c r="J38" s="9" t="str">
+      <c r="K38" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B38,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B38))</f>
         <v/>
       </c>
-      <c r="K38" s="9" t="str">
+      <c r="L38" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B38,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B38))</f>
         <v/>
       </c>
-      <c r="L38" s="10" t="n">
-        <f aca="false">SUM(E38,G38,I38,K38)</f>
+      <c r="M38" s="11" t="n">
+        <f aca="false">SUM(F38,H38,J38,L38)</f>
         <v>0</v>
       </c>
-      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
         <v>8</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="9" t="str">
+        <v>80</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B39,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B39))</f>
         <v/>
       </c>
-      <c r="E39" s="9" t="str">
+      <c r="F39" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B39,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B39))</f>
         <v/>
       </c>
-      <c r="F39" s="9" t="str">
+      <c r="G39" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B39,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B39))</f>
         <v/>
       </c>
-      <c r="G39" s="9" t="str">
+      <c r="H39" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B39,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B39))</f>
         <v/>
       </c>
-      <c r="H39" s="9" t="str">
+      <c r="I39" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B39,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B39))</f>
         <v/>
       </c>
-      <c r="I39" s="9" t="str">
+      <c r="J39" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B39,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B39))</f>
         <v/>
       </c>
-      <c r="J39" s="9" t="str">
+      <c r="K39" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B39,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B39))</f>
         <v/>
       </c>
-      <c r="K39" s="9" t="str">
+      <c r="L39" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B39,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B39))</f>
         <v/>
       </c>
-      <c r="L39" s="10" t="n">
-        <f aca="false">SUM(E39,G39,I39,K39)</f>
+      <c r="M39" s="11" t="n">
+        <f aca="false">SUM(F39,H39,J39,L39)</f>
         <v>0</v>
       </c>
-      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
         <v>9</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="9" t="str">
+        <v>81</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B40,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B40))</f>
         <v/>
       </c>
-      <c r="E40" s="9" t="str">
+      <c r="F40" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B40,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B40))</f>
         <v/>
       </c>
-      <c r="F40" s="9" t="str">
+      <c r="G40" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B40,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B40))</f>
         <v/>
       </c>
-      <c r="G40" s="9" t="str">
+      <c r="H40" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B40,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B40))</f>
         <v/>
       </c>
-      <c r="H40" s="9" t="str">
+      <c r="I40" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B40,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B40))</f>
         <v/>
       </c>
-      <c r="I40" s="9" t="str">
+      <c r="J40" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B40,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B40))</f>
         <v/>
       </c>
-      <c r="J40" s="9" t="str">
+      <c r="K40" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B40,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B40))</f>
         <v/>
       </c>
-      <c r="K40" s="9" t="str">
+      <c r="L40" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B40,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B40))</f>
         <v/>
       </c>
-      <c r="L40" s="10" t="n">
-        <f aca="false">SUM(E40,G40,I40,K40)</f>
+      <c r="M40" s="11" t="n">
+        <f aca="false">SUM(F40,H40,J40,L40)</f>
         <v>0</v>
       </c>
-      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
         <v>10</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" s="9" t="str">
+        <v>83</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B41,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B41))</f>
         <v/>
       </c>
-      <c r="E41" s="9" t="str">
+      <c r="F41" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B41,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B41))</f>
         <v/>
       </c>
-      <c r="F41" s="9" t="str">
+      <c r="G41" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B41,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B41))</f>
         <v/>
       </c>
-      <c r="G41" s="9" t="str">
+      <c r="H41" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B41,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B41))</f>
         <v/>
       </c>
-      <c r="H41" s="9" t="str">
+      <c r="I41" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B41,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B41))</f>
         <v/>
       </c>
-      <c r="I41" s="9" t="str">
+      <c r="J41" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B41,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B41))</f>
         <v/>
       </c>
-      <c r="J41" s="9" t="str">
+      <c r="K41" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B41,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B41))</f>
         <v/>
       </c>
-      <c r="K41" s="9" t="str">
+      <c r="L41" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B41,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B41))</f>
         <v/>
       </c>
-      <c r="L41" s="10" t="n">
-        <f aca="false">SUM(E41,G41,I41,K41)</f>
+      <c r="M41" s="11" t="n">
+        <f aca="false">SUM(F41,H41,J41,L41)</f>
         <v>0</v>
       </c>
-      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
         <v>11</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" s="9" t="str">
+        <v>85</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B42,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B42))</f>
         <v/>
       </c>
-      <c r="E42" s="9" t="str">
+      <c r="F42" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B42,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B42))</f>
         <v/>
       </c>
-      <c r="F42" s="9" t="str">
+      <c r="G42" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B42,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B42))</f>
         <v/>
       </c>
-      <c r="G42" s="9" t="str">
+      <c r="H42" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B42,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B42))</f>
         <v/>
       </c>
-      <c r="H42" s="9" t="str">
+      <c r="I42" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B42,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B42))</f>
         <v/>
       </c>
-      <c r="I42" s="9" t="str">
+      <c r="J42" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B42,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B42))</f>
         <v/>
       </c>
-      <c r="J42" s="9" t="str">
+      <c r="K42" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B42,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B42))</f>
         <v/>
       </c>
-      <c r="K42" s="9" t="str">
+      <c r="L42" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B42,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B42))</f>
         <v/>
       </c>
-      <c r="L42" s="10" t="n">
-        <f aca="false">SUM(E42,G42,I42,K42)</f>
+      <c r="M42" s="11" t="n">
+        <f aca="false">SUM(F42,H42,J42,L42)</f>
         <v>0</v>
       </c>
-      <c r="M42" s="8"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
         <v>12</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="9" t="str">
+        <v>87</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B43,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B43))</f>
         <v/>
       </c>
-      <c r="E43" s="9" t="str">
+      <c r="F43" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B43,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B43))</f>
         <v/>
       </c>
-      <c r="F43" s="9" t="str">
+      <c r="G43" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B43,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B43))</f>
         <v/>
       </c>
-      <c r="G43" s="9" t="str">
+      <c r="H43" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B43,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B43))</f>
         <v/>
       </c>
-      <c r="H43" s="9" t="str">
+      <c r="I43" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B43,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B43))</f>
         <v/>
       </c>
-      <c r="I43" s="9" t="str">
+      <c r="J43" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B43,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B43))</f>
         <v/>
       </c>
-      <c r="J43" s="9" t="str">
+      <c r="K43" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B43,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B43))</f>
         <v/>
       </c>
-      <c r="K43" s="9" t="str">
+      <c r="L43" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B43,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B43))</f>
         <v/>
       </c>
-      <c r="L43" s="10" t="n">
-        <f aca="false">SUM(E43,G43,I43,K43)</f>
+      <c r="M43" s="11" t="n">
+        <f aca="false">SUM(F43,H43,J43,L43)</f>
         <v>0</v>
       </c>
-      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
         <v>13</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="9" t="str">
+        <v>89</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B44,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B44))</f>
         <v/>
       </c>
-      <c r="E44" s="9" t="str">
+      <c r="F44" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B44,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B44))</f>
         <v/>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="G44" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B44,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B44))</f>
         <v>75.6</v>
       </c>
-      <c r="G44" s="9" t="str">
+      <c r="H44" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B44,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B44))</f>
         <v/>
       </c>
-      <c r="H44" s="9" t="n">
+      <c r="I44" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B44,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B44))</f>
         <v>94.5</v>
       </c>
-      <c r="I44" s="9" t="str">
+      <c r="J44" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B44,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B44))</f>
         <v/>
       </c>
-      <c r="J44" s="9" t="n">
+      <c r="K44" s="10" t="n">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B44,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B44))</f>
         <v>94.5</v>
       </c>
-      <c r="K44" s="9" t="str">
+      <c r="L44" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B44,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B44))</f>
         <v/>
       </c>
-      <c r="L44" s="10" t="n">
-        <f aca="false">SUM(E44,G44,I44,K44)</f>
+      <c r="M44" s="11" t="n">
+        <f aca="false">SUM(F44,H44,J44,L44)</f>
         <v>0</v>
       </c>
-      <c r="M44" s="11" t="s">
-        <v>61</v>
+      <c r="N44" s="9" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4509,206 +5600,219 @@
         <v>14</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="9" t="str">
+        <v>91</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B45,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B45))</f>
         <v/>
       </c>
-      <c r="E45" s="9" t="str">
+      <c r="F45" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B45,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B45))</f>
         <v/>
       </c>
-      <c r="F45" s="9" t="str">
+      <c r="G45" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B45,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B45))</f>
         <v/>
       </c>
-      <c r="G45" s="9" t="str">
+      <c r="H45" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B45,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B45))</f>
         <v/>
       </c>
-      <c r="H45" s="9" t="str">
+      <c r="I45" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B45,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B45))</f>
         <v/>
       </c>
-      <c r="I45" s="9" t="str">
+      <c r="J45" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B45,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B45))</f>
         <v/>
       </c>
-      <c r="J45" s="9" t="str">
+      <c r="K45" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B45,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B45))</f>
         <v/>
       </c>
-      <c r="K45" s="9" t="str">
+      <c r="L45" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B45,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B45))</f>
         <v/>
       </c>
-      <c r="L45" s="10" t="n">
-        <f aca="false">SUM(E45,G45,I45,K45)</f>
+      <c r="M45" s="11" t="n">
+        <f aca="false">SUM(F45,H45,J45,L45)</f>
         <v>0</v>
       </c>
-      <c r="M45" s="8"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N45" s="8"/>
+    </row>
+    <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
         <v>15</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="9" t="str">
+        <v>93</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B46,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B46))</f>
         <v/>
       </c>
-      <c r="E46" s="9" t="str">
+      <c r="F46" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B46,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B46))</f>
         <v/>
       </c>
-      <c r="F46" s="9" t="str">
+      <c r="G46" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B46,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B46))</f>
         <v/>
       </c>
-      <c r="G46" s="9" t="str">
+      <c r="H46" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B46,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B46))</f>
         <v/>
       </c>
-      <c r="H46" s="9" t="str">
+      <c r="I46" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B46,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B46))</f>
         <v/>
       </c>
-      <c r="I46" s="9" t="str">
+      <c r="J46" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B46,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B46))</f>
         <v/>
       </c>
-      <c r="J46" s="9" t="str">
+      <c r="K46" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B46,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B46))</f>
         <v/>
       </c>
-      <c r="K46" s="9" t="str">
+      <c r="L46" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B46,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B46))</f>
         <v/>
       </c>
-      <c r="L46" s="10" t="n">
-        <f aca="false">SUM(E46,G46,I46,K46)</f>
+      <c r="M46" s="11" t="n">
+        <f aca="false">SUM(F46,H46,J46,L46)</f>
         <v>0</v>
       </c>
-      <c r="M46" s="8"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N46" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
         <v>16</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" s="9" t="str">
+        <v>95</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B47,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B47))</f>
         <v/>
       </c>
-      <c r="E47" s="9" t="str">
+      <c r="F47" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B47,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B47))</f>
         <v/>
       </c>
-      <c r="F47" s="9" t="str">
+      <c r="G47" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B47,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B47))</f>
         <v/>
       </c>
-      <c r="G47" s="9" t="str">
+      <c r="H47" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B47,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B47))</f>
         <v/>
       </c>
-      <c r="H47" s="9" t="str">
+      <c r="I47" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B47,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B47))</f>
         <v/>
       </c>
-      <c r="I47" s="9" t="str">
+      <c r="J47" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B47,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B47))</f>
         <v/>
       </c>
-      <c r="J47" s="9" t="str">
+      <c r="K47" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B47,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B47))</f>
         <v/>
       </c>
-      <c r="K47" s="9" t="str">
+      <c r="L47" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B47,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B47))</f>
         <v/>
       </c>
-      <c r="L47" s="10" t="n">
-        <f aca="false">SUM(E47,G47,I47,K47)</f>
+      <c r="M47" s="11" t="n">
+        <f aca="false">SUM(F47,H47,J47,L47)</f>
         <v>0</v>
       </c>
-      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
         <v>17</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="9" t="str">
+        <v>97</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B48,'North Light'!$E$6:$E$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$E$6:$E$38,'North Light'!$B$6:$B$38,$B48))</f>
         <v/>
       </c>
-      <c r="E48" s="9" t="str">
+      <c r="F48" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Light'!$B$6:$B$38,$B48,'North Light'!$F$6:$F$38,"&lt;&gt;")=0,"",SUMIFS('North Light'!$F$6:$F$38,'North Light'!$B$6:$B$38,$B48))</f>
         <v/>
       </c>
-      <c r="F48" s="9" t="str">
+      <c r="G48" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B48,'North Moon'!$E$6:$E$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$E$6:$E$13,'North Moon'!$B$6:$B$13,$B48))</f>
         <v/>
       </c>
-      <c r="G48" s="9" t="str">
+      <c r="H48" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Moon'!$B$6:$B$13,$B48,'North Moon'!$F$6:$F$13,"&lt;&gt;")=0,"",SUMIFS('North Moon'!$F$6:$F$13,'North Moon'!$B$6:$B$13,$B48))</f>
         <v/>
       </c>
-      <c r="H48" s="9" t="str">
+      <c r="I48" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B48,'North Ocean'!$E$6:$E$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$E$6:$E$17,'North Ocean'!$B$6:$B$17,$B48))</f>
         <v/>
       </c>
-      <c r="I48" s="9" t="str">
+      <c r="J48" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Ocean'!$B$6:$B$17,$B48,'North Ocean'!$F$6:$F$17,"&lt;&gt;")=0,"",SUMIFS('North Ocean'!$F$6:$F$17,'North Ocean'!$B$6:$B$17,$B48))</f>
         <v/>
       </c>
-      <c r="J48" s="9" t="str">
+      <c r="K48" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B48,'North Valley'!$E$6:$E$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$E$6:$E$22,'North Valley'!$B$6:$B$22,$B48))</f>
         <v/>
       </c>
-      <c r="K48" s="9" t="str">
+      <c r="L48" s="10" t="str">
         <f aca="false">IF(COUNTIFS('North Valley'!$B$6:$B$22,$B48,'North Valley'!$F$6:$F$22,"&lt;&gt;")=0,"",SUMIFS('North Valley'!$F$6:$F$22,'North Valley'!$B$6:$B$22,$B48))</f>
         <v/>
       </c>
-      <c r="L48" s="10" t="n">
-        <f aca="false">SUM(E48,G48,I48,K48)</f>
+      <c r="M48" s="11" t="n">
+        <f aca="false">SUM(F48,H48,J48,L48)</f>
         <v>0</v>
       </c>
-      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
     <mergeCell ref="M6:M7"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="A8:N8"/>
+    <mergeCell ref="A31:N31"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4739,17 +5843,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>67</v>
+      <c r="A2" s="13" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>68</v>
+      <c r="A3" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4760,27 +5864,27 @@
         <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -4795,73 +5899,73 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>72</v>
+        <v>21</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="9" t="n">
-        <f aca="false">8*'통합 청구'!$C$3</f>
+        <v>23</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="10" t="n">
+        <f aca="false">8*'통합 청구'!$D$3</f>
         <v>160</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>75</v>
+        <v>24</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="9" t="n">
-        <f aca="false">6*'통합 청구'!$C$3</f>
+        <v>23</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="10" t="n">
+        <f aca="false">6*'통합 청구'!$D$3</f>
         <v>120</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>78</v>
+        <v>26</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15" t="n">
         <v>108</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4869,48 +5973,48 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>80</v>
+        <v>33</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="9" t="n">
-        <f aca="false">9*'통합 청구'!$C$3</f>
+        <v>23</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="10" t="n">
+        <f aca="false">9*'통합 청구'!$D$3</f>
         <v>180</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>83</v>
+        <v>37</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15" t="n">
         <v>108</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4918,48 +6022,48 @@
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>84</v>
+        <v>42</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="9" t="n">
-        <f aca="false">2*'통합 청구'!$C$3</f>
+        <v>23</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="10" t="n">
+        <f aca="false">2*'통합 청구'!$D$3</f>
         <v>40</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="15" t="n">
         <v>40</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4967,21 +6071,21 @@
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>90</v>
+        <v>48</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="9" t="n">
-        <f aca="false">2*'통합 청구'!$C$3</f>
+        <v>23</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="10" t="n">
+        <f aca="false">2*'통합 청구'!$D$3</f>
         <v>40</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="H14" s="8"/>
     </row>
@@ -4990,24 +6094,24 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>91</v>
+        <v>52</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="9" t="n">
-        <f aca="false">3*'통합 청구'!$C$4</f>
+        <v>28</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="10" t="n">
+        <f aca="false">3*'통합 청구'!$D$4</f>
         <v>54</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5015,31 +6119,31 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E16" s="15" t="n">
         <f aca="false">21250+740+3690</f>
         <v>25680</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="15" t="n">
         <v>21000</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -5049,21 +6153,21 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>98</v>
+        <v>66</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
@@ -5072,16 +6176,16 @@
         <v>2</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
@@ -5090,34 +6194,34 @@
         <v>3</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>100</v>
+        <v>70</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
+        <v>28</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>101</v>
+        <v>35</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+        <v>28</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
@@ -5126,16 +6230,16 @@
         <v>5</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>102</v>
+        <v>40</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
     </row>
@@ -5144,70 +6248,70 @@
         <v>6</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>103</v>
+        <v>72</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
     </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
         <v>7</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>104</v>
+        <v>74</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
-    <row r="25" customFormat="false" ht="47.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
         <v>8</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>105</v>
+        <v>46</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
         <v>9</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
     </row>
@@ -5216,19 +6320,19 @@
         <v>10</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
+        <v>28</v>
+      </c>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5236,19 +6340,19 @@
         <v>11</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
+        <v>28</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5256,19 +6360,19 @@
         <v>12</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>109</v>
+        <v>81</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>82</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5276,52 +6380,52 @@
         <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>111</v>
+        <v>83</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
         <v>15</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>113</v>
+        <v>87</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
@@ -5330,16 +6434,16 @@
         <v>16</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
@@ -5348,36 +6452,36 @@
         <v>17</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
+        <v>28</v>
+      </c>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="47.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
         <v>18</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>117</v>
+        <v>91</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
@@ -5386,39 +6490,39 @@
         <v>19</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>118</v>
+        <v>93</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
       <c r="G36" s="8"/>
       <c r="H36" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="36.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
         <v>20</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>120</v>
+        <v>95</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>96</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5426,16 +6530,16 @@
         <v>21</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
     </row>
@@ -5473,17 +6577,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>124</v>
+      <c r="A2" s="13" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>68</v>
+      <c r="A3" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5494,27 +6598,27 @@
         <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -5529,42 +6633,46 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>22</v>
+      </c>
       <c r="D7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E7" s="15" t="n">
         <v>106</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <v>200</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="8"/>
+        <v>24</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="D8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>120</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <v>300</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H8" s="8"/>
     </row>
@@ -5573,20 +6681,22 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="8"/>
+        <v>42</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="D9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H9" s="8"/>
     </row>
@@ -5595,23 +6705,25 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="D10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E10" s="15" t="n">
         <v>25080</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <v>30000</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5619,30 +6731,30 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>131</v>
+        <v>62</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>100</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H11" s="11" t="s">
         <v>133</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -5657,22 +6769,24 @@
         <v>1</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="8"/>
+        <v>89</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="D13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <f aca="false">4*'통합 청구'!$C$5</f>
+        <v>23</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <f aca="false">4*'통합 청구'!$D$5</f>
         <v>75.6</v>
       </c>
-      <c r="F13" s="13"/>
+      <c r="F13" s="14"/>
       <c r="G13" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -5709,17 +6823,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>138</v>
+      <c r="A2" s="13" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>68</v>
+      <c r="A3" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5730,27 +6844,27 @@
         <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -5760,25 +6874,25 @@
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>140</v>
+        <v>24</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15" t="n">
         <v>120</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H7" s="8"/>
     </row>
@@ -5787,18 +6901,18 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>142</v>
+        <v>33</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <v>40</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -5808,23 +6922,23 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>142</v>
+        <v>35</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>72</v>
       </c>
       <c r="G9" s="8" t="s">
@@ -5834,23 +6948,23 @@
         <v>146</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>142</v>
+        <v>37</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="15" t="n">
         <v>52</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <v>90</v>
       </c>
       <c r="G10" s="8" t="s">
@@ -5860,23 +6974,23 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>20</v>
       </c>
       <c r="G11" s="8" t="s">
@@ -5886,21 +7000,21 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>151</v>
+        <v>48</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="15" t="n">
         <v>40</v>
       </c>
       <c r="G12" s="8" t="s">
@@ -5908,30 +7022,30 @@
       </c>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>152</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>400</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5939,20 +7053,20 @@
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15" t="n">
         <v>15000</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H14" s="8"/>
     </row>
@@ -5961,30 +7075,30 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>131</v>
+        <v>62</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E15" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="15" t="n">
         <v>120</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -5999,22 +7113,24 @@
         <v>1</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="8"/>
+        <v>89</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="D17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <f aca="false">5*'통합 청구'!$C$5</f>
+        <v>23</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <f aca="false">5*'통합 청구'!$D$5</f>
         <v>94.5</v>
       </c>
-      <c r="F17" s="13"/>
+      <c r="F17" s="14"/>
       <c r="G17" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>136</v>
+        <v>155</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -6051,17 +7167,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>159</v>
+      <c r="A2" s="13" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>68</v>
+      <c r="A3" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6072,27 +7188,27 @@
         <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -6107,24 +7223,26 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="8"/>
+        <v>26</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>27</v>
+      </c>
       <c r="D7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E7" s="15" t="n">
         <v>140</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <f aca="false">3*18</f>
         <v>54</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6132,24 +7250,26 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="D8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <f aca="false">2*18</f>
         <v>36</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6157,48 +7277,52 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="8"/>
+        <v>31</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="D9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>100</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="D10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <f aca="false">10*18</f>
         <v>180</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6206,23 +7330,25 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="8"/>
+        <v>39</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="D11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>160</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6230,71 +7356,77 @@
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="8"/>
+        <v>40</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="D12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="15" t="n">
         <v>100</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="8"/>
+        <v>44</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="D13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="15" t="n">
         <v>60</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="8"/>
+        <v>46</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="D14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="15" t="n">
         <v>60</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6302,23 +7434,25 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="8"/>
+        <v>48</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>49</v>
+      </c>
       <c r="D15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E15" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="15" t="n">
         <v>20</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6326,23 +7460,25 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="8"/>
+        <v>50</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="D16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="15" t="n">
         <v>18</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6350,24 +7486,26 @@
         <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="8"/>
+        <v>51</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="D17" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E17" s="15" t="n">
         <v>102</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="15" t="n">
         <f aca="false">5*18</f>
         <v>90</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6375,24 +7513,26 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="8"/>
+        <v>56</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="D18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="15" t="n">
         <f aca="false">0.38*5</f>
         <v>1.9</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6400,20 +7540,22 @@
         <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="D19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E19" s="15" t="n">
         <v>19500</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="15" t="n">
         <v>45000</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H19" s="8"/>
     </row>
@@ -6422,31 +7564,31 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>131</v>
+        <v>62</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="15" t="n">
         <f aca="false">4*18.9</f>
         <v>75.6</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -6461,22 +7603,24 @@
         <v>1</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="8"/>
+        <v>89</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="D22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <f aca="false">5*'통합 청구'!$C$5</f>
+        <v>23</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <f aca="false">5*'통합 청구'!$D$5</f>
         <v>94.5</v>
       </c>
-      <c r="F22" s="13"/>
+      <c r="F22" s="14"/>
       <c r="G22" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>136</v>
+        <v>155</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
